--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128968127</v>
       </c>
       <c r="B2" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128968141</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128968127</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128968141</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128968127</v>
       </c>
       <c r="B2" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128968141</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>128968004</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45242-2025 artfynd.xlsx
+++ b/artfynd/A 45242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968141</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>